--- a/04_DESIGN_TABLES/DesignTable_2404L.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2404L.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1011,24 +1016,47 @@
           <t>2404-L-32-32</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.375</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2404-L-32-32</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (JIC) x 2-11 1/2 (NPTF) long pattern</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_2404-L-32-32.stp, every value equal to the catalog within 0.005); end details from the end library: L20@DRIVE: Brennan TFA catalog p.6 table TFA-p006-t03 "2404-L MJ-MP STRAIGHT LONG" row 2404-L-32-32 col "L LGTH" = "5.620" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 529.3, page verified True) [Brennan = yes 2026-10-18] - overall length; own STEP: overall 5.6204 (bbox -1.3332 .. 4.2872, C_ownstep/measure/2404-L-32-32.txt + 2404-L-32-32_axial_section.txt (nptfm40.py, jicm.py, axial section)); CHEX@HEX: Brennan TFA catalog p.6 table TFA-p006-t03 "2404-L MJ-MP STRAIGHT LONG" row 2404-L-32-32 col "C HEX" = "2.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 529.3, page verified True) [Brennan = yes 2026-10-18] - body hex; own STEP: hex corner radius 1.5158 = A/F 2.6254, hex 0 .. 3.257 (C_ownstep/measure/2404-L-32-32.txt + 2404-L-32-32_axial_section.txt (nptfm40.py, jicm.py, axial section)); D@BORE: Brennan TFA catalog p.6 table TFA-p006-t03 "2404-L MJ-MP STRAIGHT LONG" row 2404-L-32-32 col "B1 DRILL" = "1.781" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 529.3, page verified True) [Brennan = yes 2026-10-18] - JIC-end bore; own STEP: bore 1.781 from the JIC tip to 1.6285 = the hex mid-plane (C_ownstep/measure/2404-L-32-32.txt + 2404-L-32-32_axial_section.txt (nptfm40.py, jicm.py, axial section)); D1@BORE: Brennan TFA catalog p.6 table TFA-p006-t03 "2404-L MJ-MP STRAIGHT LONG" row 2404-L-32-32 col "A2 DRILL" = "1.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 529.3, page verified True) [Brennan = yes 2026-10-18] - pipe-end bore; own STEP: bore 1.938 from the hex mid-plane to the pipe tip (C_ownstep/measure/2404-L-32-32.txt + 2404-L-32-32_axial_section.txt (nptfm40.py, jicm.py, axial section)) - confirms the "likely" pairing of wave 2 and the generator rule "two bores stepped at the hex mid-plane" (Q-2404-BORE 2026-10-09); THDMAJ_B@DRIVE: end library: male JIC -32 thread major = 2.5 (gen_straight2 JIC[32] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] (own STEP: JIC end 1.333 = the -32 chain: TM 2.5, SL 0.3318, CD 2.38, LL 0.1292, TZ 0.7124, RL 0.125); THDMAJ_A@DRIVE: end library: pipe OD of the -32 NPTF thread = 2.375 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[32]) [Q-TRANSFER-ENDLIB yes 2026-10-08] (own STEP: collar 2.375, male NPTF end 1.03 = ENDL[32])</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way prints no -32 2404-L row</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1039,6 +1067,11 @@
       <c r="O11" t="inlineStr">
         <is>
           <t>2404-L-32-32</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
